--- a/Decks/Ool.xlsx
+++ b/Decks/Ool.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Dropbox\Jogos\Magic\Decks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AF9C015-6ACF-4D68-A3C6-F03DF25C892F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6AA05A6-56DF-4595-8ACE-AF975016683C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{549E3075-0D87-4429-83C3-89BC362436D3}"/>
   </bookViews>
@@ -344,9 +344,6 @@
     <t>Wickerbough Elder</t>
   </si>
   <si>
-    <t>Dusk Uchins</t>
-  </si>
-  <si>
     <t>Lasting Tarfire</t>
   </si>
   <si>
@@ -384,6 +381,9 @@
   </si>
   <si>
     <t>Tree of Perdition</t>
+  </si>
+  <si>
+    <t>Dusk Urchins</t>
   </si>
 </sst>
 </file>
@@ -1010,7 +1010,7 @@
         <v>1</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D15" t="s">
         <v>76</v>
@@ -1025,7 +1025,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D16" t="s">
         <v>80</v>
@@ -1682,10 +1682,10 @@
         <v>0</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F59"/>
     </row>
@@ -1698,7 +1698,7 @@
         <v>1</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D60" t="s">
         <v>74</v>
@@ -1762,7 +1762,7 @@
         <v>1</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D64" t="s">
         <v>73</v>
@@ -1858,7 +1858,7 @@
         <v>1</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D70" s="4" t="s">
         <v>85</v>
@@ -1874,7 +1874,7 @@
         <v>1</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D71" t="s">
         <v>50</v>
@@ -1891,7 +1891,7 @@
         <v>1</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D72" s="4" t="s">
         <v>91</v>
@@ -2095,7 +2095,7 @@
         <v>1</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D84" s="4" t="s">
         <v>48</v>
@@ -2145,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="D87" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="E87" s="4"/>
       <c r="F87"/>
@@ -2162,10 +2162,10 @@
         <v>0</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F88"/>
     </row>
@@ -2178,7 +2178,7 @@
         <v>1</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D89" s="4" t="s">
         <v>94</v>
@@ -2194,10 +2194,10 @@
         <v>0</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F90"/>
     </row>
@@ -2226,10 +2226,10 @@
         <v>0</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F92"/>
     </row>

--- a/Decks/Ool.xlsx
+++ b/Decks/Ool.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Dropbox\Jogos\TheMagicCollection\Decks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6AA05A6-56DF-4595-8ACE-AF975016683C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F577BED9-3C30-443D-9751-6310ECD5AE2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{549E3075-0D87-4429-83C3-89BC362436D3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{549E3075-0D87-4429-83C3-89BC362436D3}"/>
   </bookViews>
   <sheets>
     <sheet name="Ool" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="115">
   <si>
     <t>Função</t>
   </si>
@@ -356,9 +356,6 @@
     <t>Contagion Clasp</t>
   </si>
   <si>
-    <t>Bogslither's Embrace</t>
-  </si>
-  <si>
     <t>Persist</t>
   </si>
   <si>
@@ -374,9 +371,6 @@
     <t>Cauldron of Souls</t>
   </si>
   <si>
-    <t>Unnatural Restoration</t>
-  </si>
-  <si>
     <t>Gnarlbark Elm</t>
   </si>
   <si>
@@ -384,6 +378,9 @@
   </si>
   <si>
     <t>Dusk Urchins</t>
+  </si>
+  <si>
+    <t>Grim Affliction</t>
   </si>
 </sst>
 </file>
@@ -1010,7 +1007,7 @@
         <v>1</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D15" t="s">
         <v>76</v>
@@ -1025,7 +1022,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D16" t="s">
         <v>80</v>
@@ -1698,7 +1695,7 @@
         <v>1</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="D60" t="s">
         <v>74</v>
@@ -1858,7 +1855,7 @@
         <v>1</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D70" s="4" t="s">
         <v>85</v>
@@ -1871,10 +1868,10 @@
       </c>
       <c r="B71" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>112</v>
+        <v>50</v>
       </c>
       <c r="D71" t="s">
         <v>50</v>
@@ -1891,7 +1888,7 @@
         <v>1</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D72" s="4" t="s">
         <v>91</v>
@@ -2095,7 +2092,7 @@
         <v>1</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D84" s="4" t="s">
         <v>48</v>
@@ -2145,10 +2142,10 @@
         <v>0</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D87" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E87" s="4"/>
       <c r="F87"/>
@@ -2178,7 +2175,7 @@
         <v>1</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D89" s="4" t="s">
         <v>94</v>
@@ -2194,10 +2191,10 @@
         <v>0</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F90"/>
     </row>

--- a/Decks/Ool.xlsx
+++ b/Decks/Ool.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F577BED9-3C30-443D-9751-6310ECD5AE2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2113149-D321-4B61-94AB-2B2208E918B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{549E3075-0D87-4429-83C3-89BC362436D3}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="113">
   <si>
     <t>Função</t>
   </si>
@@ -176,9 +176,6 @@
     <t>Cankerbloom</t>
   </si>
   <si>
-    <t>Chain Reaction</t>
-  </si>
-  <si>
     <t>Marcador</t>
   </si>
   <si>
@@ -345,9 +342,6 @@
   </si>
   <si>
     <t>Lasting Tarfire</t>
-  </si>
-  <si>
-    <t>Infernal Grasp</t>
   </si>
   <si>
     <t>Puncture Blast</t>
@@ -857,10 +851,10 @@
         <v>0</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -1007,10 +1001,10 @@
         <v>1</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D15" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -1022,10 +1016,10 @@
         <v>1</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1037,10 +1031,10 @@
         <v>0</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1082,10 +1076,10 @@
         <v>0</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D20" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1097,10 +1091,10 @@
         <v>0</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D21" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1130,7 +1124,7 @@
         <v>24</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1145,7 +1139,7 @@
         <v>24</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1157,10 +1151,10 @@
         <v>0</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1442,10 +1436,10 @@
         <v>0</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -1473,10 +1467,10 @@
         <v>0</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F46"/>
     </row>
@@ -1489,10 +1483,10 @@
         <v>0</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -1504,10 +1498,10 @@
         <v>0</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -1519,10 +1513,10 @@
         <v>0</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F49"/>
     </row>
@@ -1567,10 +1561,10 @@
         <v>0</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F52"/>
     </row>
@@ -1624,39 +1618,39 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B56" s="5" t="b">
         <f>C56&lt;&gt;D56</f>
         <v>0</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D56" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F56"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B57" s="5" t="b">
         <f>C57&lt;&gt;D57</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F57"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B58" s="5" t="b">
         <f>C58&lt;&gt;D58</f>
@@ -1679,10 +1673,10 @@
         <v>0</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F59"/>
     </row>
@@ -1695,10 +1689,10 @@
         <v>1</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D60" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F60"/>
     </row>
@@ -1756,13 +1750,13 @@
       </c>
       <c r="B64" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>103</v>
+        <v>72</v>
       </c>
       <c r="D64" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F64" s="4"/>
     </row>
@@ -1775,10 +1769,10 @@
         <v>0</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F65" s="4"/>
     </row>
@@ -1791,10 +1785,10 @@
         <v>0</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D66" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F66" s="4"/>
     </row>
@@ -1823,558 +1817,558 @@
         <v>0</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D68" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F68" s="4"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B69" s="5" t="b">
         <f t="shared" ref="B69:B101" si="1">C69&lt;&gt;D69</f>
         <v>0</v>
       </c>
       <c r="C69" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F69" s="4"/>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B70" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F70" s="4"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B71" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D71" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E71" s="4"/>
       <c r="F71" s="4"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B72" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E72" s="4"/>
       <c r="F72" s="4"/>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B73" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E73" s="4"/>
       <c r="F73" s="4"/>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B74" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D74" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E74" s="4"/>
       <c r="F74" s="4"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B75" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E75" s="4"/>
       <c r="F75" s="4"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B76" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E76" s="4"/>
       <c r="F76" s="4"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B77" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E77" s="4"/>
       <c r="F77" s="4"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B78" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E78" s="4"/>
       <c r="F78" s="4"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B79" s="5" t="b">
         <f>C79&lt;&gt;D79</f>
         <v>0</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E79" s="4"/>
       <c r="F79" s="4"/>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B80" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E80" s="4"/>
       <c r="F80"/>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B81" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E81" s="4"/>
       <c r="F81"/>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B82" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E82" s="4"/>
       <c r="F82"/>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B83" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E83" s="4"/>
       <c r="F83"/>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B84" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E84" s="4"/>
       <c r="F84"/>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B85" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E85" s="4"/>
       <c r="F85"/>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B86" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F86"/>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B87" s="5" t="b">
         <f>C87&lt;&gt;D87</f>
         <v>0</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D87" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E87" s="4"/>
       <c r="F87"/>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B88" s="5" t="b">
         <f>C88&lt;&gt;D88</f>
         <v>0</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F88"/>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B89" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F89"/>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B90" s="5" t="b">
         <f>C90&lt;&gt;D90</f>
         <v>0</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F90"/>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B91" s="5" t="b">
         <f>C91&lt;&gt;D91</f>
         <v>0</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F91" s="4"/>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B92" s="5" t="b">
         <f>C92&lt;&gt;D92</f>
         <v>0</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F92"/>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B93" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E93" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F93"/>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B94" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F94"/>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B95" s="5" t="b">
         <f>C95&lt;&gt;D95</f>
         <v>0</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E95" s="4"/>
       <c r="F95"/>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B96" s="5" t="b">
         <f>C96&lt;&gt;D96</f>
         <v>0</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F96"/>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B97" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F97"/>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B98" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F98"/>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B99" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F99"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B100" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F100"/>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B101" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F101"/>
     </row>

--- a/Decks/Ool.xlsx
+++ b/Decks/Ool.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2113149-D321-4B61-94AB-2B2208E918B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CFAAF6E-38D2-4F93-9626-C37271134BA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{549E3075-0D87-4429-83C3-89BC362436D3}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="110">
   <si>
     <t>Função</t>
   </si>
@@ -218,9 +218,6 @@
     <t>Hapatra, Vizier of Poisons</t>
   </si>
   <si>
-    <t>Heirloom Auntie</t>
-  </si>
-  <si>
     <t>Flourishing Defenses</t>
   </si>
   <si>
@@ -356,18 +353,9 @@
     <t>Path of Ancestry</t>
   </si>
   <si>
-    <t>Savage Lands</t>
-  </si>
-  <si>
     <t>Thrull Parasite</t>
   </si>
   <si>
-    <t>Cauldron of Souls</t>
-  </si>
-  <si>
-    <t>Gnarlbark Elm</t>
-  </si>
-  <si>
     <t>Tree of Perdition</t>
   </si>
   <si>
@@ -375,6 +363,9 @@
   </si>
   <si>
     <t>Grim Affliction</t>
+  </si>
+  <si>
+    <t>Mister Hyde, Monster Within</t>
   </si>
 </sst>
 </file>
@@ -817,7 +808,7 @@
         <v>8</v>
       </c>
       <c r="B3" s="5" t="b">
-        <f t="shared" ref="B3:B68" si="0">C3&lt;&gt;D3</f>
+        <f t="shared" ref="B3:B69" si="0">C3&lt;&gt;D3</f>
         <v>0</v>
       </c>
       <c r="C3" s="4" t="s">
@@ -851,10 +842,10 @@
         <v>0</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -998,13 +989,13 @@
       </c>
       <c r="B15" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>106</v>
+        <v>74</v>
       </c>
       <c r="D15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -1016,10 +1007,10 @@
         <v>1</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D16" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1031,10 +1022,10 @@
         <v>0</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D17" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1091,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D21" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1118,13 +1109,13 @@
       </c>
       <c r="B23" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>24</v>
+        <v>93</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1133,13 +1124,13 @@
       </c>
       <c r="B24" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>24</v>
+        <v>94</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1151,10 +1142,10 @@
         <v>0</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1436,10 +1427,10 @@
         <v>0</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -1467,10 +1458,10 @@
         <v>0</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F46"/>
     </row>
@@ -1483,10 +1474,10 @@
         <v>0</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -1498,10 +1489,10 @@
         <v>0</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -1513,10 +1504,10 @@
         <v>0</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F49"/>
     </row>
@@ -1561,10 +1552,10 @@
         <v>0</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F52"/>
     </row>
@@ -1573,15 +1564,16 @@
         <v>34</v>
       </c>
       <c r="B53" s="5" t="b">
-        <f t="shared" si="0"/>
+        <f>C53&lt;&gt;D53</f>
         <v>0</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>37</v>
+        <v>109</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>37</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="E53" s="4"/>
       <c r="F53"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -1593,10 +1585,10 @@
         <v>0</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F54"/>
     </row>
@@ -1609,76 +1601,76 @@
         <v>0</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F55"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="B56" s="5" t="b">
-        <f>C56&lt;&gt;D56</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="D56" t="s">
-        <v>77</v>
+        <v>39</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>39</v>
       </c>
       <c r="F56"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B57" s="5" t="b">
         <f>C57&lt;&gt;D57</f>
         <v>0</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D57" s="4" t="s">
-        <v>68</v>
+        <v>76</v>
+      </c>
+      <c r="D57" t="s">
+        <v>76</v>
       </c>
       <c r="F57"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B58" s="5" t="b">
         <f>C58&lt;&gt;D58</f>
         <v>0</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="F58" s="4"/>
+        <v>67</v>
+      </c>
+      <c r="F58"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="B59" s="5" t="b">
         <f>C59&lt;&gt;D59</f>
         <v>0</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>102</v>
+        <v>44</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="F59"/>
+        <v>44</v>
+      </c>
+      <c r="F59" s="4"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
@@ -1686,13 +1678,13 @@
       </c>
       <c r="B60" s="5" t="b">
         <f>C60&lt;&gt;D60</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="D60" t="s">
-        <v>73</v>
+        <v>101</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>101</v>
       </c>
       <c r="F60"/>
     </row>
@@ -1701,16 +1693,16 @@
         <v>40</v>
       </c>
       <c r="B61" s="5" t="b">
-        <f t="shared" si="0"/>
+        <f>C61&lt;&gt;D61</f>
         <v>0</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D61" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="F61" s="4"/>
+        <v>72</v>
+      </c>
+      <c r="D61" t="s">
+        <v>72</v>
+      </c>
+      <c r="F61"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
@@ -1721,10 +1713,10 @@
         <v>0</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F62" s="4"/>
     </row>
@@ -1737,10 +1729,10 @@
         <v>0</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F63" s="4"/>
     </row>
@@ -1753,10 +1745,10 @@
         <v>0</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="D64" t="s">
-        <v>72</v>
+        <v>43</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>43</v>
       </c>
       <c r="F64" s="4"/>
     </row>
@@ -1769,10 +1761,10 @@
         <v>0</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="D65" s="4" t="s">
-        <v>88</v>
+        <v>71</v>
+      </c>
+      <c r="D65" t="s">
+        <v>71</v>
       </c>
       <c r="F65" s="4"/>
     </row>
@@ -1785,10 +1777,10 @@
         <v>0</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="D66" t="s">
-        <v>76</v>
+        <v>87</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>87</v>
       </c>
       <c r="F66" s="4"/>
     </row>
@@ -1801,10 +1793,10 @@
         <v>0</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D67" s="4" t="s">
-        <v>45</v>
+        <v>75</v>
+      </c>
+      <c r="D67" t="s">
+        <v>75</v>
       </c>
       <c r="F67" s="4"/>
     </row>
@@ -1817,26 +1809,26 @@
         <v>0</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="D68" t="s">
-        <v>100</v>
+        <v>45</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>45</v>
       </c>
       <c r="F68" s="4"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B69" s="5" t="b">
-        <f t="shared" ref="B69:B101" si="1">C69&lt;&gt;D69</f>
-        <v>0</v>
-      </c>
-      <c r="C69" t="s">
-        <v>97</v>
-      </c>
-      <c r="D69" s="4" t="s">
-        <v>97</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="D69" t="s">
+        <v>99</v>
       </c>
       <c r="F69" s="4"/>
     </row>
@@ -1845,14 +1837,14 @@
         <v>46</v>
       </c>
       <c r="B70" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C70" s="4" t="s">
-        <v>110</v>
+        <f t="shared" ref="B70:B101" si="1">C70&lt;&gt;D70</f>
+        <v>0</v>
+      </c>
+      <c r="C70" t="s">
+        <v>96</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="F70" s="4"/>
     </row>
@@ -1865,12 +1857,11 @@
         <v>0</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D71" t="s">
-        <v>49</v>
-      </c>
-      <c r="E71" s="4"/>
+        <v>83</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>83</v>
+      </c>
       <c r="F71" s="4"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -1879,13 +1870,13 @@
       </c>
       <c r="B72" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="D72" s="4" t="s">
-        <v>90</v>
+        <v>49</v>
+      </c>
+      <c r="D72" t="s">
+        <v>49</v>
       </c>
       <c r="E72" s="4"/>
       <c r="F72" s="4"/>
@@ -1896,13 +1887,13 @@
       </c>
       <c r="B73" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>71</v>
+        <v>108</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="E73" s="4"/>
       <c r="F73" s="4"/>
@@ -1916,10 +1907,10 @@
         <v>0</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D74" t="s">
-        <v>52</v>
+        <v>70</v>
+      </c>
+      <c r="D74" s="4" t="s">
+        <v>70</v>
       </c>
       <c r="E74" s="4"/>
       <c r="F74" s="4"/>
@@ -1933,10 +1924,10 @@
         <v>0</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="D75" s="4" t="s">
-        <v>85</v>
+        <v>52</v>
+      </c>
+      <c r="D75" t="s">
+        <v>52</v>
       </c>
       <c r="E75" s="4"/>
       <c r="F75" s="4"/>
@@ -1950,10 +1941,10 @@
         <v>0</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>53</v>
+        <v>84</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>53</v>
+        <v>84</v>
       </c>
       <c r="E76" s="4"/>
       <c r="F76" s="4"/>
@@ -1967,10 +1958,10 @@
         <v>0</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E77" s="4"/>
       <c r="F77" s="4"/>
@@ -1984,10 +1975,10 @@
         <v>0</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E78" s="4"/>
       <c r="F78" s="4"/>
@@ -1997,14 +1988,14 @@
         <v>46</v>
       </c>
       <c r="B79" s="5" t="b">
-        <f>C79&lt;&gt;D79</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="E79" s="4"/>
       <c r="F79" s="4"/>
@@ -2014,17 +2005,17 @@
         <v>46</v>
       </c>
       <c r="B80" s="5" t="b">
-        <f t="shared" si="1"/>
+        <f>C80&lt;&gt;D80</f>
         <v>0</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E80" s="4"/>
-      <c r="F80"/>
+      <c r="F80" s="4"/>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
@@ -2035,10 +2026,10 @@
         <v>0</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E81" s="4"/>
       <c r="F81"/>
@@ -2052,10 +2043,10 @@
         <v>0</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E82" s="4"/>
       <c r="F82"/>
@@ -2086,7 +2077,7 @@
         <v>1</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D84" s="4" t="s">
         <v>47</v>
@@ -2136,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D87" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E87" s="4"/>
       <c r="F87"/>
@@ -2153,10 +2144,10 @@
         <v>0</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F88"/>
     </row>
@@ -2169,10 +2160,10 @@
         <v>1</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F89"/>
     </row>
@@ -2185,10 +2176,10 @@
         <v>0</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F90"/>
     </row>
@@ -2201,10 +2192,10 @@
         <v>0</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F91" s="4"/>
     </row>
@@ -2217,10 +2208,10 @@
         <v>0</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F92"/>
     </row>
@@ -2233,13 +2224,13 @@
         <v>0</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E93" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F93"/>
     </row>
@@ -2285,10 +2276,10 @@
         <v>0</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F96"/>
     </row>
@@ -2301,10 +2292,10 @@
         <v>0</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F97"/>
     </row>
@@ -2317,10 +2308,10 @@
         <v>0</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F98"/>
     </row>
@@ -2333,10 +2324,10 @@
         <v>0</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F99"/>
     </row>
@@ -2349,10 +2340,10 @@
         <v>0</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F100"/>
     </row>
@@ -2365,10 +2356,10 @@
         <v>0</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F101"/>
     </row>
